--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/monitoring_items_i_chart_template.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/monitoring_items_i_chart_template.xlsx
@@ -222,32 +222,32 @@
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析结果预览</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析结果预览</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析结果预览</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析结果预览</t>
         </is>
       </c>
       <c r="G2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析结果预览</t>
         </is>
       </c>
       <c r="H2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析结果预览</t>
         </is>
       </c>
       <c r="I2" t="inlineStr" s="2">
@@ -333,32 +333,32 @@
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">新增监控项目</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">新增监控项目</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">新增监控项目</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">新增监控项目</t>
         </is>
       </c>
       <c r="G3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">新增监控项目</t>
         </is>
       </c>
       <c r="H3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">新增监控项目</t>
         </is>
       </c>
       <c r="I3" t="inlineStr" s="2">
@@ -443,32 +443,32 @@
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">变量带出</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">变量带出</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">变量带出</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">变量带出</t>
         </is>
       </c>
       <c r="G4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">变量带出</t>
         </is>
       </c>
       <c r="H4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">变量带出</t>
         </is>
       </c>
       <c r="I4" t="inlineStr" s="2">
@@ -670,27 +670,27 @@
       </c>
       <c r="D6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数据替换</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数据替换</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数据替换</t>
         </is>
       </c>
       <c r="G6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数据替换</t>
         </is>
       </c>
       <c r="H6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数据替换</t>
         </is>
       </c>
       <c r="I6" t="inlineStr" s="2">
@@ -895,27 +895,27 @@
       </c>
       <c r="D8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数据处理</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数据处理</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数据处理</t>
         </is>
       </c>
       <c r="G8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数据处理</t>
         </is>
       </c>
       <c r="H8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数据处理</t>
         </is>
       </c>
       <c r="I8" t="inlineStr" s="2">
@@ -1122,22 +1122,22 @@
       </c>
       <c r="E10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">定类变量暂不支持分析</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">定类变量暂不支持分析</t>
         </is>
       </c>
       <c r="G10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">定类变量暂不支持分析</t>
         </is>
       </c>
       <c r="H10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">定类变量暂不支持分析</t>
         </is>
       </c>
       <c r="I10" t="inlineStr" s="2">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="E12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析字段有删减</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析字段有删减</t>
         </is>
       </c>
       <c r="G12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析字段有删减</t>
         </is>
       </c>
       <c r="H12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析字段有删减</t>
         </is>
       </c>
       <c r="I12" t="inlineStr" s="2">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="E14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考线的阶段未匹配上</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考线的阶段未匹配上</t>
         </is>
       </c>
       <c r="G14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考线的阶段未匹配上</t>
         </is>
       </c>
       <c r="H14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考线的阶段未匹配上</t>
         </is>
       </c>
       <c r="I14" t="inlineStr" s="2">
@@ -1786,22 +1786,22 @@
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">其他原因</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">其他原因</t>
         </is>
       </c>
       <c r="G16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">其他原因</t>
         </is>
       </c>
       <c r="H16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">其他原因</t>
         </is>
       </c>
       <c r="I16" t="inlineStr" s="2">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="E18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">提示优先级</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">提示优先级</t>
         </is>
       </c>
       <c r="G18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">提示优先级</t>
         </is>
       </c>
       <c r="H18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">提示优先级</t>
         </is>
       </c>
       <c r="I18" t="inlineStr" s="2">
@@ -2446,27 +2446,27 @@
       </c>
       <c r="D22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">未分析的图参与一键分析</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">未分析的图参与一键分析</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">未分析的图参与一键分析</t>
         </is>
       </c>
       <c r="G22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">未分析的图参与一键分析</t>
         </is>
       </c>
       <c r="H22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">未分析的图参与一键分析</t>
         </is>
       </c>
       <c r="I22" t="inlineStr" s="2">
@@ -3109,27 +3109,27 @@
       </c>
       <c r="D28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">正常一键分析校验</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">正常一键分析校验</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">正常一键分析校验</t>
         </is>
       </c>
       <c r="G28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">正常一键分析校验</t>
         </is>
       </c>
       <c r="H28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">正常一键分析校验</t>
         </is>
       </c>
       <c r="I28" t="inlineStr" s="2">
@@ -3432,37 +3432,37 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">相关性分析</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">相关性分析</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">相关性分析</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">相关性分析</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">相关性分析</t>
         </is>
       </c>
       <c r="G31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">相关性分析</t>
         </is>
       </c>
       <c r="H31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">相关性分析</t>
         </is>
       </c>
       <c r="I31" t="inlineStr" s="2">
@@ -3551,27 +3551,27 @@
       </c>
       <c r="D32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">配置项</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">配置项</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">配置项</t>
         </is>
       </c>
       <c r="G32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">配置项</t>
         </is>
       </c>
       <c r="H32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">配置项</t>
         </is>
       </c>
       <c r="I32" t="inlineStr" s="2">
@@ -3669,22 +3669,22 @@
       </c>
       <c r="E33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">放入纵轴定量变量</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">放入纵轴定量变量</t>
         </is>
       </c>
       <c r="G33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">放入纵轴定量变量</t>
         </is>
       </c>
       <c r="H33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">放入纵轴定量变量</t>
         </is>
       </c>
       <c r="I33" t="inlineStr" s="2">
@@ -4434,22 +4434,22 @@
       </c>
       <c r="E40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">放入横轴变量</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">放入横轴变量</t>
         </is>
       </c>
       <c r="G40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">放入横轴变量</t>
         </is>
       </c>
       <c r="H40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">放入横轴变量</t>
         </is>
       </c>
       <c r="I40" t="inlineStr" s="2">
@@ -4654,22 +4654,22 @@
       </c>
       <c r="E42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">估算标准差</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">估算标准差</t>
         </is>
       </c>
       <c r="G42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">估算标准差</t>
         </is>
       </c>
       <c r="H42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">估算标准差</t>
         </is>
       </c>
       <c r="I42" t="inlineStr" s="2">
@@ -4870,22 +4870,22 @@
       </c>
       <c r="E44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">横轴旋转角度</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">横轴旋转角度</t>
         </is>
       </c>
       <c r="G44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">横轴旋转角度</t>
         </is>
       </c>
       <c r="H44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">横轴旋转角度</t>
         </is>
       </c>
       <c r="I44" t="inlineStr" s="2">
@@ -4980,22 +4980,22 @@
       </c>
       <c r="E45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">纵轴范围</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">纵轴范围</t>
         </is>
       </c>
       <c r="G45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">纵轴范围</t>
         </is>
       </c>
       <c r="H45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">纵轴范围</t>
         </is>
       </c>
       <c r="I45" t="inlineStr" s="2">
@@ -5198,22 +5198,22 @@
       </c>
       <c r="E47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置</t>
         </is>
       </c>
       <c r="G47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置</t>
         </is>
       </c>
       <c r="H47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置</t>
         </is>
       </c>
       <c r="I47" t="inlineStr" s="2">
@@ -5308,22 +5308,22 @@
       </c>
       <c r="E48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">阶段</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">阶段</t>
         </is>
       </c>
       <c r="G48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">阶段</t>
         </is>
       </c>
       <c r="H48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">阶段</t>
         </is>
       </c>
       <c r="I48" t="inlineStr" s="2">
@@ -6292,22 +6292,22 @@
       </c>
       <c r="E57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">显示设置</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">显示设置</t>
         </is>
       </c>
       <c r="G57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">显示设置</t>
         </is>
       </c>
       <c r="H57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">显示设置</t>
         </is>
       </c>
       <c r="I57" t="inlineStr" s="2">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="G58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考线类型</t>
         </is>
       </c>
       <c r="H58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考线类型</t>
         </is>
       </c>
       <c r="I58" t="inlineStr" s="2">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="G61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考线名称</t>
         </is>
       </c>
       <c r="H61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考线名称</t>
         </is>
       </c>
       <c r="I61" t="inlineStr" s="2">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="H62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考值</t>
         </is>
       </c>
       <c r="I62" t="inlineStr" s="2">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="H68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">偏移</t>
         </is>
       </c>
       <c r="I68" t="inlineStr" s="2">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="H71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">启用判异</t>
         </is>
       </c>
       <c r="I71" t="inlineStr" s="2">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="H72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数据类型</t>
         </is>
       </c>
       <c r="I72" t="inlineStr" s="2">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="H97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为自定义参考限生效范围</t>
         </is>
       </c>
       <c r="I97" t="inlineStr" s="2">
@@ -10793,12 +10793,12 @@
       </c>
       <c r="G98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">选择判异参考线</t>
         </is>
       </c>
       <c r="H98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">选择判异参考线</t>
         </is>
       </c>
       <c r="I98" t="inlineStr" s="2">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="H99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为用此变量定义阶段</t>
         </is>
       </c>
       <c r="I99" t="inlineStr" s="2">
@@ -11005,17 +11005,17 @@
       </c>
       <c r="F100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">添加参考限</t>
         </is>
       </c>
       <c r="G100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">添加参考限</t>
         </is>
       </c>
       <c r="H100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">添加参考限</t>
         </is>
       </c>
       <c r="I100" t="inlineStr" s="2">
@@ -11113,17 +11113,17 @@
       </c>
       <c r="F101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考线列表</t>
         </is>
       </c>
       <c r="G101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考线列表</t>
         </is>
       </c>
       <c r="H101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考线列表</t>
         </is>
       </c>
       <c r="I101" t="inlineStr" s="2">
@@ -11555,17 +11555,17 @@
       </c>
       <c r="F105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">编辑</t>
         </is>
       </c>
       <c r="G105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">编辑</t>
         </is>
       </c>
       <c r="H105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">编辑</t>
         </is>
       </c>
       <c r="I105" t="inlineStr" s="2">
@@ -11893,12 +11893,12 @@
       </c>
       <c r="G108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">编辑判异参考线(自定义参考限生效范围)</t>
         </is>
       </c>
       <c r="H108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">编辑判异参考线(自定义参考限生效范围)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr" s="2">
@@ -12332,17 +12332,17 @@
       </c>
       <c r="F112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">删除</t>
         </is>
       </c>
       <c r="G112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">删除</t>
         </is>
       </c>
       <c r="H112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">删除</t>
         </is>
       </c>
       <c r="I112" t="inlineStr" s="2">
@@ -12545,22 +12545,22 @@
       </c>
       <c r="E114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">判异检查</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">判异检查</t>
         </is>
       </c>
       <c r="G114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">判异检查</t>
         </is>
       </c>
       <c r="H114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">判异检查</t>
         </is>
       </c>
       <c r="I114" t="inlineStr" s="2">
@@ -12665,17 +12665,17 @@
       </c>
       <c r="F115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">8 项判异配置项检查</t>
         </is>
       </c>
       <c r="G115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">8 项判异配置项检查</t>
         </is>
       </c>
       <c r="H115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">8 项判异配置项检查</t>
         </is>
       </c>
       <c r="I115" t="inlineStr" s="2">
@@ -13524,22 +13524,22 @@
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">判异检查</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">判异检查</t>
         </is>
       </c>
       <c r="G123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">判异检查</t>
         </is>
       </c>
       <c r="H123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">判异检查</t>
         </is>
       </c>
       <c r="I123" t="inlineStr" s="2">
@@ -13740,22 +13740,22 @@
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">小数位数</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">小数位数</t>
         </is>
       </c>
       <c r="G125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">小数位数</t>
         </is>
       </c>
       <c r="H125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">小数位数</t>
         </is>
       </c>
       <c r="I125" t="inlineStr" s="2">
@@ -13848,22 +13848,22 @@
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析流程</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析流程</t>
         </is>
       </c>
       <c r="G126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析流程</t>
         </is>
       </c>
       <c r="H126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析流程</t>
         </is>
       </c>
       <c r="I126" t="inlineStr" s="2">
@@ -14288,22 +14288,22 @@
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析图</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析图</t>
         </is>
       </c>
       <c r="G130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析图</t>
         </is>
       </c>
       <c r="H130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析图</t>
         </is>
       </c>
       <c r="I130" t="inlineStr" s="2">
@@ -14401,17 +14401,17 @@
       </c>
       <c r="F131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">阶段显示</t>
         </is>
       </c>
       <c r="G131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">阶段显示</t>
         </is>
       </c>
       <c r="H131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">阶段显示</t>
         </is>
       </c>
       <c r="I131" t="inlineStr" s="2">
@@ -14622,17 +14622,17 @@
       </c>
       <c r="F133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">纵轴范围</t>
         </is>
       </c>
       <c r="G133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">纵轴范围</t>
         </is>
       </c>
       <c r="H133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">纵轴范围</t>
         </is>
       </c>
       <c r="I133" t="inlineStr" s="2">
@@ -14838,17 +14838,17 @@
       </c>
       <c r="F135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">横轴变量</t>
         </is>
       </c>
       <c r="G135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">横轴变量</t>
         </is>
       </c>
       <c r="H135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">横轴变量</t>
         </is>
       </c>
       <c r="I135" t="inlineStr" s="2">
@@ -15164,17 +15164,17 @@
       </c>
       <c r="F138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">横轴旋转角度</t>
         </is>
       </c>
       <c r="G138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">横轴旋转角度</t>
         </is>
       </c>
       <c r="H138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">横轴旋转角度</t>
         </is>
       </c>
       <c r="I138" t="inlineStr" s="2">
@@ -15488,17 +15488,17 @@
       </c>
       <c r="F141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">显示设置</t>
         </is>
       </c>
       <c r="G141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">显示设置</t>
         </is>
       </c>
       <c r="H141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">显示设置</t>
         </is>
       </c>
       <c r="I141" t="inlineStr" s="2">
@@ -15934,7 +15934,7 @@
       </c>
       <c r="H145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为无</t>
         </is>
       </c>
       <c r="I145" t="inlineStr" s="2">
@@ -17254,7 +17254,7 @@
       </c>
       <c r="H157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为用此变量定义阶段</t>
         </is>
       </c>
       <c r="I157" t="inlineStr" s="2">
@@ -17706,7 +17706,7 @@
       </c>
       <c r="H161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为自定义参考限生效范围</t>
         </is>
       </c>
       <c r="I161" t="inlineStr" s="2">
@@ -18149,12 +18149,12 @@
       </c>
       <c r="G165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">基准参考线</t>
         </is>
       </c>
       <c r="H165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">基准参考线</t>
         </is>
       </c>
       <c r="I165" t="inlineStr" s="2">
@@ -18364,17 +18364,17 @@
       </c>
       <c r="F167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考线设置</t>
         </is>
       </c>
       <c r="G167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考线设置</t>
         </is>
       </c>
       <c r="H167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考线设置</t>
         </is>
       </c>
       <c r="I167" t="inlineStr" s="2">
@@ -18580,17 +18580,17 @@
       </c>
       <c r="F169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考线优先级</t>
         </is>
       </c>
       <c r="G169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考线优先级</t>
         </is>
       </c>
       <c r="H169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">参考线优先级</t>
         </is>
       </c>
       <c r="I169" t="inlineStr" s="2">
@@ -19233,17 +19233,17 @@
       </c>
       <c r="F175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">观测点</t>
         </is>
       </c>
       <c r="G175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">观测点</t>
         </is>
       </c>
       <c r="H175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">观测点</t>
         </is>
       </c>
       <c r="I175" t="inlineStr" s="2">
@@ -19883,22 +19883,22 @@
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">过程数据</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">过程数据</t>
         </is>
       </c>
       <c r="G181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">过程数据</t>
         </is>
       </c>
       <c r="H181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">过程数据</t>
         </is>
       </c>
       <c r="I181" t="inlineStr" s="2">
@@ -20446,12 +20446,12 @@
       </c>
       <c r="G186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为无</t>
         </is>
       </c>
       <c r="H186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为无</t>
         </is>
       </c>
       <c r="I186" t="inlineStr" s="2">
@@ -21011,12 +21011,12 @@
       </c>
       <c r="G191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为用此变量定义阶段</t>
         </is>
       </c>
       <c r="H191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为用此变量定义阶段</t>
         </is>
       </c>
       <c r="I191" t="inlineStr" s="2">
@@ -21237,12 +21237,12 @@
       </c>
       <c r="G193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为自定义参考限生效范围</t>
         </is>
       </c>
       <c r="H193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为自定义参考限生效范围</t>
         </is>
       </c>
       <c r="I193" t="inlineStr" s="2">
@@ -21448,27 +21448,27 @@
       </c>
       <c r="D195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">联动校验</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">联动校验</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">联动校验</t>
         </is>
       </c>
       <c r="G195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">联动校验</t>
         </is>
       </c>
       <c r="H195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">联动校验</t>
         </is>
       </c>
       <c r="I195" t="inlineStr" s="2">
@@ -21666,27 +21666,27 @@
       </c>
       <c r="D197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">格式校验</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">格式校验</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">格式校验</t>
         </is>
       </c>
       <c r="G197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">格式校验</t>
         </is>
       </c>
       <c r="H197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">格式校验</t>
         </is>
       </c>
       <c r="I197" t="inlineStr" s="2">
@@ -21889,22 +21889,22 @@
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为无</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为无</t>
         </is>
       </c>
       <c r="G199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为无</t>
         </is>
       </c>
       <c r="H199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为无</t>
         </is>
       </c>
       <c r="I199" t="inlineStr" s="2">
@@ -22107,22 +22107,22 @@
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为用此变量定义阶段</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为用此变量定义阶段</t>
         </is>
       </c>
       <c r="G201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为用此变量定义阶段</t>
         </is>
       </c>
       <c r="H201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为用此变量定义阶段</t>
         </is>
       </c>
       <c r="I201" t="inlineStr" s="2">
@@ -22327,22 +22327,22 @@
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为自定义参考限生效范围</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为自定义参考限生效范围</t>
         </is>
       </c>
       <c r="G203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为自定义参考限生效范围</t>
         </is>
       </c>
       <c r="H203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">排列配置为自定义参考限生效范围</t>
         </is>
       </c>
       <c r="I203" t="inlineStr" s="2">
@@ -22545,22 +22545,22 @@
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">场景</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">场景</t>
         </is>
       </c>
       <c r="G205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">场景</t>
         </is>
       </c>
       <c r="H205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">场景</t>
         </is>
       </c>
       <c r="I205" t="inlineStr" s="2">
@@ -22649,27 +22649,27 @@
       </c>
       <c r="D206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">自定义结论</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">自定义结论</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">自定义结论</t>
         </is>
       </c>
       <c r="G206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">自定义结论</t>
         </is>
       </c>
       <c r="H206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">自定义结论</t>
         </is>
       </c>
       <c r="I206" t="inlineStr" s="2">
@@ -22868,27 +22868,27 @@
       </c>
       <c r="D208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析图生成</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析图生成</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析图生成</t>
         </is>
       </c>
       <c r="G208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析图生成</t>
         </is>
       </c>
       <c r="H208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">分析图生成</t>
         </is>
       </c>
       <c r="I208" t="inlineStr" s="2">
@@ -22988,17 +22988,17 @@
       </c>
       <c r="F209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">时分秒</t>
         </is>
       </c>
       <c r="G209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">时分秒</t>
         </is>
       </c>
       <c r="H209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">时分秒</t>
         </is>
       </c>
       <c r="I209" t="inlineStr" s="2">
@@ -23318,17 +23318,17 @@
       </c>
       <c r="F212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数值</t>
         </is>
       </c>
       <c r="G212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数值</t>
         </is>
       </c>
       <c r="H212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">数值</t>
         </is>
       </c>
       <c r="I212" t="inlineStr" s="2">
@@ -23864,22 +23864,22 @@
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">异常情况</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">异常情况</t>
         </is>
       </c>
       <c r="G217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">异常情况</t>
         </is>
       </c>
       <c r="H217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">异常情况</t>
         </is>
       </c>
       <c r="I217" t="inlineStr" s="2">
@@ -24194,22 +24194,22 @@
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">小数位修改影响范围</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">小数位修改影响范围</t>
         </is>
       </c>
       <c r="G220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">小数位修改影响范围</t>
         </is>
       </c>
       <c r="H220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">小数位修改影响范围</t>
         </is>
       </c>
       <c r="I220" t="inlineStr" s="2">
@@ -24739,22 +24739,22 @@
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">小数位修改不影响范围</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">小数位修改不影响范围</t>
         </is>
       </c>
       <c r="G225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">小数位修改不影响范围</t>
         </is>
       </c>
       <c r="H225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">小数位修改不影响范围</t>
         </is>
       </c>
       <c r="I225" t="inlineStr" s="2">
@@ -25170,27 +25170,27 @@
       </c>
       <c r="D229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">更改配置</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">更改配置</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">更改配置</t>
         </is>
       </c>
       <c r="G229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">更改配置</t>
         </is>
       </c>
       <c r="H229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">更改配置</t>
         </is>
       </c>
       <c r="I229" t="inlineStr" s="2">
@@ -25379,37 +25379,37 @@
       </c>
       <c r="B231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">报告</t>
         </is>
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">报告</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">报告</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">报告</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">报告</t>
         </is>
       </c>
       <c r="G231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">报告</t>
         </is>
       </c>
       <c r="H231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">报告</t>
         </is>
       </c>
       <c r="I231" t="inlineStr" s="2">

--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/monitoring_items_i_chart_template.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/monitoring_items_i_chart_template.xlsx
@@ -222,32 +222,32 @@
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析结果预览</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析结果预览</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析结果预览</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析结果预览</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析结果预览</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析结果预览</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I2" t="inlineStr" s="2">
@@ -333,32 +333,32 @@
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">新增监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">新增监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">新增监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">新增监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">新增监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">新增监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I3" t="inlineStr" s="2">
@@ -443,32 +443,32 @@
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">变量带出</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">变量带出</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">变量带出</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">变量带出</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">变量带出</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">变量带出</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I4" t="inlineStr" s="2">
@@ -670,27 +670,27 @@
       </c>
       <c r="D6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据替换</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据替换</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据替换</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据替换</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据替换</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I6" t="inlineStr" s="2">
@@ -895,27 +895,27 @@
       </c>
       <c r="D8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据处理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据处理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据处理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据处理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据处理</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I8" t="inlineStr" s="2">
@@ -1122,22 +1122,22 @@
       </c>
       <c r="E10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">定类变量暂不支持分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">定类变量暂不支持分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">定类变量暂不支持分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">定类变量暂不支持分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I10" t="inlineStr" s="2">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="E12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析字段有删减</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析字段有删减</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析字段有删减</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析字段有删减</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I12" t="inlineStr" s="2">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="E14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线的阶段未匹配上</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线的阶段未匹配上</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线的阶段未匹配上</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线的阶段未匹配上</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I14" t="inlineStr" s="2">
@@ -1786,22 +1786,22 @@
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">其他原因</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">其他原因</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">其他原因</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">其他原因</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I16" t="inlineStr" s="2">
@@ -2007,22 +2007,22 @@
       </c>
       <c r="E18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">提示优先级</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">提示优先级</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">提示优先级</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">提示优先级</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I18" t="inlineStr" s="2">
@@ -2446,27 +2446,27 @@
       </c>
       <c r="D22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">未分析的图参与一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">未分析的图参与一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">未分析的图参与一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">未分析的图参与一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">未分析的图参与一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I22" t="inlineStr" s="2">
@@ -3109,27 +3109,27 @@
       </c>
       <c r="D28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">正常一键分析校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">正常一键分析校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">正常一键分析校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">正常一键分析校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">正常一键分析校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I28" t="inlineStr" s="2">
@@ -3432,37 +3432,37 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">相关性分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">相关性分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">相关性分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">相关性分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">相关性分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">相关性分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">相关性分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I31" t="inlineStr" s="2">
@@ -3551,27 +3551,27 @@
       </c>
       <c r="D32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I32" t="inlineStr" s="2">
@@ -3669,22 +3669,22 @@
       </c>
       <c r="E33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">放入纵轴定量变量</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">放入纵轴定量变量</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">放入纵轴定量变量</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">放入纵轴定量变量</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I33" t="inlineStr" s="2">
@@ -4434,22 +4434,22 @@
       </c>
       <c r="E40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">放入横轴变量</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">放入横轴变量</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">放入横轴变量</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">放入横轴变量</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I40" t="inlineStr" s="2">
@@ -4654,22 +4654,22 @@
       </c>
       <c r="E42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">估算标准差</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">估算标准差</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">估算标准差</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">估算标准差</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I42" t="inlineStr" s="2">
@@ -4870,22 +4870,22 @@
       </c>
       <c r="E44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">横轴旋转角度</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">横轴旋转角度</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">横轴旋转角度</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">横轴旋转角度</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I44" t="inlineStr" s="2">
@@ -4980,22 +4980,22 @@
       </c>
       <c r="E45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">纵轴范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">纵轴范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">纵轴范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">纵轴范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I45" t="inlineStr" s="2">
@@ -5198,22 +5198,22 @@
       </c>
       <c r="E47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I47" t="inlineStr" s="2">
@@ -5308,22 +5308,22 @@
       </c>
       <c r="E48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">阶段</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">阶段</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">阶段</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">阶段</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I48" t="inlineStr" s="2">
@@ -6292,22 +6292,22 @@
       </c>
       <c r="E57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">显示设置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">显示设置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">显示设置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">显示设置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I57" t="inlineStr" s="2">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="G58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线类型</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线类型</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I58" t="inlineStr" s="2">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="G61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线名称</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线名称</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I61" t="inlineStr" s="2">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="H62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考值</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I62" t="inlineStr" s="2">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="H68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">偏移</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I68" t="inlineStr" s="2">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="H71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">启用判异</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I71" t="inlineStr" s="2">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="H72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据类型</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I72" t="inlineStr" s="2">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="H97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为自定义参考限生效范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I97" t="inlineStr" s="2">
@@ -10793,12 +10793,12 @@
       </c>
       <c r="G98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">选择判异参考线</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">选择判异参考线</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I98" t="inlineStr" s="2">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="H99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为用此变量定义阶段</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I99" t="inlineStr" s="2">
@@ -11005,17 +11005,17 @@
       </c>
       <c r="F100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">添加参考限</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">添加参考限</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">添加参考限</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I100" t="inlineStr" s="2">
@@ -11113,17 +11113,17 @@
       </c>
       <c r="F101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线列表</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线列表</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线列表</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I101" t="inlineStr" s="2">
@@ -11555,17 +11555,17 @@
       </c>
       <c r="F105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">编辑</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">编辑</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">编辑</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I105" t="inlineStr" s="2">
@@ -11893,12 +11893,12 @@
       </c>
       <c r="G108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">编辑判异参考线(自定义参考限生效范围)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">编辑判异参考线(自定义参考限生效范围)</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I108" t="inlineStr" s="2">
@@ -12332,17 +12332,17 @@
       </c>
       <c r="F112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">删除</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">删除</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">删除</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I112" t="inlineStr" s="2">
@@ -12545,22 +12545,22 @@
       </c>
       <c r="E114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">判异检查</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">判异检查</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">判异检查</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">判异检查</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I114" t="inlineStr" s="2">
@@ -12665,17 +12665,17 @@
       </c>
       <c r="F115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8 项判异配置项检查</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8 项判异配置项检查</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">8 项判异配置项检查</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I115" t="inlineStr" s="2">
@@ -13524,22 +13524,22 @@
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">判异检查</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">判异检查</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">判异检查</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">判异检查</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I123" t="inlineStr" s="2">
@@ -13740,22 +13740,22 @@
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小数位数</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小数位数</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小数位数</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小数位数</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I125" t="inlineStr" s="2">
@@ -13848,22 +13848,22 @@
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析流程</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析流程</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析流程</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析流程</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I126" t="inlineStr" s="2">
@@ -14288,22 +14288,22 @@
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I130" t="inlineStr" s="2">
@@ -14401,17 +14401,17 @@
       </c>
       <c r="F131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">阶段显示</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">阶段显示</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">阶段显示</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I131" t="inlineStr" s="2">
@@ -14622,17 +14622,17 @@
       </c>
       <c r="F133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">纵轴范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">纵轴范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">纵轴范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I133" t="inlineStr" s="2">
@@ -14838,17 +14838,17 @@
       </c>
       <c r="F135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">横轴变量</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">横轴变量</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">横轴变量</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I135" t="inlineStr" s="2">
@@ -15164,17 +15164,17 @@
       </c>
       <c r="F138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">横轴旋转角度</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">横轴旋转角度</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">横轴旋转角度</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I138" t="inlineStr" s="2">
@@ -15488,17 +15488,17 @@
       </c>
       <c r="F141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">显示设置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">显示设置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">显示设置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I141" t="inlineStr" s="2">
@@ -15934,7 +15934,7 @@
       </c>
       <c r="H145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为无</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I145" t="inlineStr" s="2">
@@ -17254,7 +17254,7 @@
       </c>
       <c r="H157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为用此变量定义阶段</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I157" t="inlineStr" s="2">
@@ -17706,7 +17706,7 @@
       </c>
       <c r="H161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为自定义参考限生效范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I161" t="inlineStr" s="2">
@@ -18149,12 +18149,12 @@
       </c>
       <c r="G165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">基准参考线</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">基准参考线</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I165" t="inlineStr" s="2">
@@ -18364,17 +18364,17 @@
       </c>
       <c r="F167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线设置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线设置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线设置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I167" t="inlineStr" s="2">
@@ -18580,17 +18580,17 @@
       </c>
       <c r="F169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线优先级</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线优先级</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线优先级</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I169" t="inlineStr" s="2">
@@ -19233,17 +19233,17 @@
       </c>
       <c r="F175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">观测点</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">观测点</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">观测点</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I175" t="inlineStr" s="2">
@@ -19883,22 +19883,22 @@
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">过程数据</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">过程数据</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">过程数据</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">过程数据</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I181" t="inlineStr" s="2">
@@ -20446,12 +20446,12 @@
       </c>
       <c r="G186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为无</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为无</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I186" t="inlineStr" s="2">
@@ -21011,12 +21011,12 @@
       </c>
       <c r="G191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为用此变量定义阶段</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为用此变量定义阶段</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I191" t="inlineStr" s="2">
@@ -21237,12 +21237,12 @@
       </c>
       <c r="G193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为自定义参考限生效范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为自定义参考限生效范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I193" t="inlineStr" s="2">
@@ -21448,27 +21448,27 @@
       </c>
       <c r="D195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">联动校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">联动校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">联动校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">联动校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">联动校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I195" t="inlineStr" s="2">
@@ -21666,27 +21666,27 @@
       </c>
       <c r="D197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">格式校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">格式校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">格式校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">格式校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">格式校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I197" t="inlineStr" s="2">
@@ -21889,22 +21889,22 @@
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为无</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为无</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为无</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为无</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I199" t="inlineStr" s="2">
@@ -22107,22 +22107,22 @@
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为用此变量定义阶段</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为用此变量定义阶段</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为用此变量定义阶段</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为用此变量定义阶段</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I201" t="inlineStr" s="2">
@@ -22327,22 +22327,22 @@
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为自定义参考限生效范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为自定义参考限生效范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为自定义参考限生效范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">排列配置为自定义参考限生效范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I203" t="inlineStr" s="2">
@@ -22545,22 +22545,22 @@
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">场景</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">场景</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">场景</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">场景</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I205" t="inlineStr" s="2">
@@ -22649,27 +22649,27 @@
       </c>
       <c r="D206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自定义结论</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自定义结论</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自定义结论</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自定义结论</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自定义结论</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I206" t="inlineStr" s="2">
@@ -22868,27 +22868,27 @@
       </c>
       <c r="D208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图生成</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图生成</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图生成</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图生成</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图生成</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I208" t="inlineStr" s="2">
@@ -22988,17 +22988,17 @@
       </c>
       <c r="F209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">时分秒</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">时分秒</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">时分秒</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I209" t="inlineStr" s="2">
@@ -23318,17 +23318,17 @@
       </c>
       <c r="F212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数值</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数值</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数值</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I212" t="inlineStr" s="2">
@@ -23864,22 +23864,22 @@
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">异常情况</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">异常情况</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">异常情况</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">异常情况</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I217" t="inlineStr" s="2">
@@ -24194,22 +24194,22 @@
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小数位修改影响范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小数位修改影响范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小数位修改影响范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小数位修改影响范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I220" t="inlineStr" s="2">
@@ -24739,22 +24739,22 @@
       </c>
       <c r="E225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小数位修改不影响范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小数位修改不影响范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小数位修改不影响范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">小数位修改不影响范围</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I225" t="inlineStr" s="2">
@@ -25170,27 +25170,27 @@
       </c>
       <c r="D229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">更改配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">更改配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">更改配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">更改配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">更改配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I229" t="inlineStr" s="2">
@@ -25379,37 +25379,37 @@
       </c>
       <c r="B231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">报告</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">报告</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">报告</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">报告</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">报告</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">报告</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">报告</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I231" t="inlineStr" s="2">
